--- a/app/templates_excel/nigredo/n7_hermetic_en.xlsx
+++ b/app/templates_excel/nigredo/n7_hermetic_en.xlsx
@@ -1188,10 +1188,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A window at an open grave.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A bridge being built across a gorge.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1448,10 +1444,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Chinese woman nusing a baby with a message.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>One hand slightly flexed with a very prominent thumb.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1576,10 +1568,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A pagent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Sunshine just after a storm.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2340,10 +2328,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A tree feiled and sawed.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Butterfly emerging from a chrysalis.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2420,10 +2404,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A gigatic tent.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>A master instructing his pupil.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2444,10 +2424,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>An inhibited island.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The purging of the priesthood.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2621,6 +2597,30 @@
   </si>
   <si>
     <t>A professor peering over his glasses.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tree felled and sawed.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A gigantic tent.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chinese woman nursing a baby with a message.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A widow at an open grave.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A pageant.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>An inhabited island.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3438,7 +3438,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -3459,50 +3459,50 @@
     </row>
     <row r="4" spans="1:17" ht="15" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="15" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="15" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>719</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>720</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="I8" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="J8" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="L8" s="5" t="s">
         <v>725</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>726</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>727</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>729</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>731</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>344</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="9" spans="1:17" ht="15" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>345</v>
@@ -3518,7 +3518,7 @@
     </row>
     <row r="10" spans="1:17" ht="15" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>346</v>
@@ -3750,42 +3750,42 @@
     </row>
     <row r="39" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A40" s="9" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="M40" s="7" t="s">
         <v>375</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="41" spans="1:13" ht="15" x14ac:dyDescent="0.3">
       <c r="A41" s="9" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>376</v>
@@ -3820,7 +3820,7 @@
         <v>31</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>379</v>
+        <v>735</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3828,7 +3828,7 @@
         <v>32</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3836,7 +3836,7 @@
         <v>33</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3844,7 +3844,7 @@
         <v>34</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3852,7 +3852,7 @@
         <v>35</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="49" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3860,7 +3860,7 @@
         <v>36</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3868,7 +3868,7 @@
         <v>37</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3876,7 +3876,7 @@
         <v>38</v>
       </c>
       <c r="M51" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3884,7 +3884,7 @@
         <v>39</v>
       </c>
       <c r="M52" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3892,7 +3892,7 @@
         <v>40</v>
       </c>
       <c r="M53" s="7" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3900,7 +3900,7 @@
         <v>41</v>
       </c>
       <c r="M54" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3908,7 +3908,7 @@
         <v>42</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3916,7 +3916,7 @@
         <v>43</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3924,7 +3924,7 @@
         <v>44</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3932,7 +3932,7 @@
         <v>45</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3940,7 +3940,7 @@
         <v>46</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3948,7 +3948,7 @@
         <v>47</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="15" x14ac:dyDescent="0.3">
@@ -3956,122 +3956,122 @@
         <v>48</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A62" s="9" t="s">
         <v>49</v>
       </c>
       <c r="M62" s="7" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A63" s="9" t="s">
         <v>50</v>
       </c>
       <c r="M63" s="7" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A64" s="9" t="s">
         <v>51</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A65" s="9" t="s">
         <v>52</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A66" s="9" t="s">
         <v>53</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A67" s="9" t="s">
         <v>54</v>
       </c>
       <c r="M67" s="7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A68" s="9" t="s">
         <v>55</v>
       </c>
       <c r="M68" s="7" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A69" s="9" t="s">
         <v>56</v>
       </c>
       <c r="M69" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="70" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L70" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A71" s="10" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="M71" s="7" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A72" s="10" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="M72" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.4">
@@ -4079,7 +4079,7 @@
         <v>57</v>
       </c>
       <c r="M73" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.4">
@@ -4087,7 +4087,7 @@
         <v>58</v>
       </c>
       <c r="M74" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.4">
@@ -4095,7 +4095,7 @@
         <v>59</v>
       </c>
       <c r="M75" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.4">
@@ -4103,7 +4103,7 @@
         <v>60</v>
       </c>
       <c r="M76" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.4">
@@ -4111,7 +4111,7 @@
         <v>61</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.4">
@@ -4119,7 +4119,7 @@
         <v>62</v>
       </c>
       <c r="M78" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.4">
@@ -4127,7 +4127,7 @@
         <v>63</v>
       </c>
       <c r="M79" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.4">
@@ -4135,7 +4135,7 @@
         <v>64</v>
       </c>
       <c r="M80" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.4">
@@ -4143,7 +4143,7 @@
         <v>65</v>
       </c>
       <c r="M81" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.4">
@@ -4151,7 +4151,7 @@
         <v>66</v>
       </c>
       <c r="M82" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.4">
@@ -4159,7 +4159,7 @@
         <v>67</v>
       </c>
       <c r="M83" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.4">
@@ -4167,7 +4167,7 @@
         <v>68</v>
       </c>
       <c r="M84" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.4">
@@ -4175,7 +4175,7 @@
         <v>69</v>
       </c>
       <c r="M85" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.4">
@@ -4183,7 +4183,7 @@
         <v>70</v>
       </c>
       <c r="M86" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.4">
@@ -4191,7 +4191,7 @@
         <v>71</v>
       </c>
       <c r="M87" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.4">
@@ -4199,7 +4199,7 @@
         <v>72</v>
       </c>
       <c r="M88" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.4">
@@ -4207,7 +4207,7 @@
         <v>73</v>
       </c>
       <c r="M89" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.4">
@@ -4215,7 +4215,7 @@
         <v>74</v>
       </c>
       <c r="M90" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.4">
@@ -4223,7 +4223,7 @@
         <v>75</v>
       </c>
       <c r="M91" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.4">
@@ -4231,7 +4231,7 @@
         <v>76</v>
       </c>
       <c r="M92" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.4">
@@ -4239,7 +4239,7 @@
         <v>77</v>
       </c>
       <c r="M93" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.4">
@@ -4247,7 +4247,7 @@
         <v>78</v>
       </c>
       <c r="M94" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.4">
@@ -4255,7 +4255,7 @@
         <v>79</v>
       </c>
       <c r="M95" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.4">
@@ -4263,7 +4263,7 @@
         <v>80</v>
       </c>
       <c r="M96" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.4">
@@ -4271,7 +4271,7 @@
         <v>81</v>
       </c>
       <c r="M97" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.4">
@@ -4279,7 +4279,7 @@
         <v>82</v>
       </c>
       <c r="M98" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.4">
@@ -4287,7 +4287,7 @@
         <v>83</v>
       </c>
       <c r="M99" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.4">
@@ -4295,50 +4295,50 @@
         <v>84</v>
       </c>
       <c r="M100" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="101" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A102" s="11" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="M102" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.4">
@@ -4346,7 +4346,7 @@
         <v>85</v>
       </c>
       <c r="M103" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.4">
@@ -4354,7 +4354,7 @@
         <v>86</v>
       </c>
       <c r="M104" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.4">
@@ -4362,7 +4362,7 @@
         <v>87</v>
       </c>
       <c r="M105" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.4">
@@ -4370,7 +4370,7 @@
         <v>88</v>
       </c>
       <c r="M106" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.4">
@@ -4378,7 +4378,7 @@
         <v>89</v>
       </c>
       <c r="M107" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.4">
@@ -4386,7 +4386,7 @@
         <v>90</v>
       </c>
       <c r="M108" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.4">
@@ -4394,7 +4394,7 @@
         <v>91</v>
       </c>
       <c r="M109" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.4">
@@ -4402,7 +4402,7 @@
         <v>92</v>
       </c>
       <c r="M110" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.4">
@@ -4410,7 +4410,7 @@
         <v>93</v>
       </c>
       <c r="M111" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.4">
@@ -4418,7 +4418,7 @@
         <v>94</v>
       </c>
       <c r="M112" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.4">
@@ -4426,7 +4426,7 @@
         <v>95</v>
       </c>
       <c r="M113" s="7" t="s">
-        <v>444</v>
+        <v>734</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.4">
@@ -4434,7 +4434,7 @@
         <v>96</v>
       </c>
       <c r="M114" s="7" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.4">
@@ -4442,7 +4442,7 @@
         <v>97</v>
       </c>
       <c r="M115" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.4">
@@ -4450,7 +4450,7 @@
         <v>98</v>
       </c>
       <c r="M116" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.4">
@@ -4458,7 +4458,7 @@
         <v>99</v>
       </c>
       <c r="M117" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.4">
@@ -4466,7 +4466,7 @@
         <v>100</v>
       </c>
       <c r="M118" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.4">
@@ -4474,7 +4474,7 @@
         <v>101</v>
       </c>
       <c r="M119" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.4">
@@ -4482,7 +4482,7 @@
         <v>102</v>
       </c>
       <c r="M120" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.4">
@@ -4490,7 +4490,7 @@
         <v>103</v>
       </c>
       <c r="M121" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.4">
@@ -4498,7 +4498,7 @@
         <v>104</v>
       </c>
       <c r="M122" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.4">
@@ -4506,7 +4506,7 @@
         <v>105</v>
       </c>
       <c r="M123" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.4">
@@ -4514,7 +4514,7 @@
         <v>106</v>
       </c>
       <c r="M124" s="7" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.4">
@@ -4522,7 +4522,7 @@
         <v>107</v>
       </c>
       <c r="M125" s="7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.4">
@@ -4530,7 +4530,7 @@
         <v>108</v>
       </c>
       <c r="M126" s="7" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.4">
@@ -4538,7 +4538,7 @@
         <v>109</v>
       </c>
       <c r="M127" s="7" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.4">
@@ -4546,7 +4546,7 @@
         <v>110</v>
       </c>
       <c r="M128" s="7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.4">
@@ -4554,7 +4554,7 @@
         <v>111</v>
       </c>
       <c r="M129" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.4">
@@ -4562,7 +4562,7 @@
         <v>112</v>
       </c>
       <c r="M130" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.4">
@@ -4570,50 +4570,50 @@
         <v>113</v>
       </c>
       <c r="M131" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="132" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L132" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A133" s="6" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="M133" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.4">
@@ -4621,7 +4621,7 @@
         <v>114</v>
       </c>
       <c r="M134" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.4">
@@ -4629,7 +4629,7 @@
         <v>115</v>
       </c>
       <c r="M135" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.4">
@@ -4637,7 +4637,7 @@
         <v>116</v>
       </c>
       <c r="M136" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.4">
@@ -4645,7 +4645,7 @@
         <v>117</v>
       </c>
       <c r="M137" s="7" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.4">
@@ -4653,7 +4653,7 @@
         <v>118</v>
       </c>
       <c r="M138" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.4">
@@ -4661,7 +4661,7 @@
         <v>119</v>
       </c>
       <c r="M139" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.4">
@@ -4669,7 +4669,7 @@
         <v>120</v>
       </c>
       <c r="M140" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.4">
@@ -4677,7 +4677,7 @@
         <v>121</v>
       </c>
       <c r="M141" s="7" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.4">
@@ -4685,7 +4685,7 @@
         <v>122</v>
       </c>
       <c r="M142" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.4">
@@ -4693,7 +4693,7 @@
         <v>123</v>
       </c>
       <c r="M143" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.4">
@@ -4701,7 +4701,7 @@
         <v>124</v>
       </c>
       <c r="M144" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.4">
@@ -4709,7 +4709,7 @@
         <v>125</v>
       </c>
       <c r="M145" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.4">
@@ -4717,7 +4717,7 @@
         <v>126</v>
       </c>
       <c r="M146" s="7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.4">
@@ -4725,7 +4725,7 @@
         <v>127</v>
       </c>
       <c r="M147" s="7" t="s">
-        <v>476</v>
+        <v>736</v>
       </c>
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.4">
@@ -4733,7 +4733,7 @@
         <v>128</v>
       </c>
       <c r="M148" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.4">
@@ -4741,7 +4741,7 @@
         <v>129</v>
       </c>
       <c r="M149" s="7" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.4">
@@ -4749,7 +4749,7 @@
         <v>130</v>
       </c>
       <c r="M150" s="7" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.4">
@@ -4757,7 +4757,7 @@
         <v>131</v>
       </c>
       <c r="M151" s="7" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.4">
@@ -4765,7 +4765,7 @@
         <v>132</v>
       </c>
       <c r="M152" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.4">
@@ -4773,7 +4773,7 @@
         <v>133</v>
       </c>
       <c r="M153" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.4">
@@ -4781,7 +4781,7 @@
         <v>134</v>
       </c>
       <c r="M154" s="7" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.4">
@@ -4789,7 +4789,7 @@
         <v>135</v>
       </c>
       <c r="M155" s="7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.4">
@@ -4797,7 +4797,7 @@
         <v>136</v>
       </c>
       <c r="M156" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.4">
@@ -4805,7 +4805,7 @@
         <v>137</v>
       </c>
       <c r="M157" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.4">
@@ -4813,7 +4813,7 @@
         <v>138</v>
       </c>
       <c r="M158" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.4">
@@ -4821,7 +4821,7 @@
         <v>139</v>
       </c>
       <c r="M159" s="7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.4">
@@ -4829,7 +4829,7 @@
         <v>140</v>
       </c>
       <c r="M160" s="7" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.4">
@@ -4837,7 +4837,7 @@
         <v>141</v>
       </c>
       <c r="M161" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.4">
@@ -4845,58 +4845,58 @@
         <v>142</v>
       </c>
       <c r="M162" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="163" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L163" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A164" s="9" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="M164" s="7" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A165" s="9" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="M165" s="7" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.4">
@@ -4904,7 +4904,7 @@
         <v>143</v>
       </c>
       <c r="M166" s="7" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.4">
@@ -4912,7 +4912,7 @@
         <v>144</v>
       </c>
       <c r="M167" s="7" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.4">
@@ -4920,7 +4920,7 @@
         <v>145</v>
       </c>
       <c r="M168" s="7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.4">
@@ -4928,7 +4928,7 @@
         <v>146</v>
       </c>
       <c r="M169" s="7" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.4">
@@ -4936,7 +4936,7 @@
         <v>147</v>
       </c>
       <c r="M170" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.4">
@@ -4944,7 +4944,7 @@
         <v>148</v>
       </c>
       <c r="M171" s="7" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.4">
@@ -4952,7 +4952,7 @@
         <v>149</v>
       </c>
       <c r="M172" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.4">
@@ -4960,7 +4960,7 @@
         <v>150</v>
       </c>
       <c r="M173" s="7" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.4">
@@ -4968,7 +4968,7 @@
         <v>151</v>
       </c>
       <c r="M174" s="7" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.4">
@@ -4976,7 +4976,7 @@
         <v>152</v>
       </c>
       <c r="M175" s="7" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.4">
@@ -4984,7 +4984,7 @@
         <v>153</v>
       </c>
       <c r="M176" s="7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.4">
@@ -4992,7 +4992,7 @@
         <v>154</v>
       </c>
       <c r="M177" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.4">
@@ -5000,7 +5000,7 @@
         <v>155</v>
       </c>
       <c r="M178" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.4">
@@ -5008,7 +5008,7 @@
         <v>156</v>
       </c>
       <c r="M179" s="7" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.4">
@@ -5016,7 +5016,7 @@
         <v>157</v>
       </c>
       <c r="M180" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.4">
@@ -5024,7 +5024,7 @@
         <v>158</v>
       </c>
       <c r="M181" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.4">
@@ -5032,7 +5032,7 @@
         <v>159</v>
       </c>
       <c r="M182" s="7" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.4">
@@ -5040,7 +5040,7 @@
         <v>160</v>
       </c>
       <c r="M183" s="7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.4">
@@ -5048,7 +5048,7 @@
         <v>161</v>
       </c>
       <c r="M184" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.4">
@@ -5056,7 +5056,7 @@
         <v>162</v>
       </c>
       <c r="M185" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.4">
@@ -5064,7 +5064,7 @@
         <v>163</v>
       </c>
       <c r="M186" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="187" spans="1:13" x14ac:dyDescent="0.4">
@@ -5072,7 +5072,7 @@
         <v>164</v>
       </c>
       <c r="M187" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="188" spans="1:13" x14ac:dyDescent="0.4">
@@ -5080,7 +5080,7 @@
         <v>165</v>
       </c>
       <c r="M188" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="189" spans="1:13" x14ac:dyDescent="0.4">
@@ -5088,7 +5088,7 @@
         <v>166</v>
       </c>
       <c r="M189" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="190" spans="1:13" x14ac:dyDescent="0.4">
@@ -5096,7 +5096,7 @@
         <v>167</v>
       </c>
       <c r="M190" s="7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="191" spans="1:13" x14ac:dyDescent="0.4">
@@ -5104,7 +5104,7 @@
         <v>168</v>
       </c>
       <c r="M191" s="7" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="192" spans="1:13" x14ac:dyDescent="0.4">
@@ -5112,7 +5112,7 @@
         <v>169</v>
       </c>
       <c r="M192" s="7" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="193" spans="1:13" x14ac:dyDescent="0.4">
@@ -5120,50 +5120,50 @@
         <v>170</v>
       </c>
       <c r="M193" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="194" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L194" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A195" s="10" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="M195" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.4">
@@ -5171,7 +5171,7 @@
         <v>171</v>
       </c>
       <c r="M196" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.4">
@@ -5179,7 +5179,7 @@
         <v>172</v>
       </c>
       <c r="M197" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.4">
@@ -5187,7 +5187,7 @@
         <v>173</v>
       </c>
       <c r="M198" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.4">
@@ -5195,7 +5195,7 @@
         <v>174</v>
       </c>
       <c r="M199" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.4">
@@ -5203,7 +5203,7 @@
         <v>175</v>
       </c>
       <c r="M200" s="7" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="201" spans="1:13" x14ac:dyDescent="0.4">
@@ -5211,7 +5211,7 @@
         <v>176</v>
       </c>
       <c r="M201" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="202" spans="1:13" x14ac:dyDescent="0.4">
@@ -5219,7 +5219,7 @@
         <v>177</v>
       </c>
       <c r="M202" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.4">
@@ -5227,7 +5227,7 @@
         <v>178</v>
       </c>
       <c r="M203" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="204" spans="1:13" x14ac:dyDescent="0.4">
@@ -5235,7 +5235,7 @@
         <v>179</v>
       </c>
       <c r="M204" s="7" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.4">
@@ -5243,7 +5243,7 @@
         <v>180</v>
       </c>
       <c r="M205" s="7" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="206" spans="1:13" x14ac:dyDescent="0.4">
@@ -5251,7 +5251,7 @@
         <v>181</v>
       </c>
       <c r="M206" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="207" spans="1:13" x14ac:dyDescent="0.4">
@@ -5259,7 +5259,7 @@
         <v>182</v>
       </c>
       <c r="M207" s="7" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="208" spans="1:13" x14ac:dyDescent="0.4">
@@ -5267,7 +5267,7 @@
         <v>183</v>
       </c>
       <c r="M208" s="7" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="209" spans="1:13" x14ac:dyDescent="0.4">
@@ -5275,7 +5275,7 @@
         <v>184</v>
       </c>
       <c r="M209" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="210" spans="1:13" x14ac:dyDescent="0.4">
@@ -5283,7 +5283,7 @@
         <v>185</v>
       </c>
       <c r="M210" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="211" spans="1:13" x14ac:dyDescent="0.4">
@@ -5291,7 +5291,7 @@
         <v>186</v>
       </c>
       <c r="M211" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.4">
@@ -5299,7 +5299,7 @@
         <v>187</v>
       </c>
       <c r="M212" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.4">
@@ -5307,7 +5307,7 @@
         <v>188</v>
       </c>
       <c r="M213" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="214" spans="1:13" x14ac:dyDescent="0.4">
@@ -5315,7 +5315,7 @@
         <v>189</v>
       </c>
       <c r="M214" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="215" spans="1:13" x14ac:dyDescent="0.4">
@@ -5323,7 +5323,7 @@
         <v>190</v>
       </c>
       <c r="M215" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="216" spans="1:13" x14ac:dyDescent="0.4">
@@ -5331,7 +5331,7 @@
         <v>191</v>
       </c>
       <c r="M216" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="217" spans="1:13" x14ac:dyDescent="0.4">
@@ -5339,7 +5339,7 @@
         <v>192</v>
       </c>
       <c r="M217" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="218" spans="1:13" x14ac:dyDescent="0.4">
@@ -5347,7 +5347,7 @@
         <v>193</v>
       </c>
       <c r="M218" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="219" spans="1:13" x14ac:dyDescent="0.4">
@@ -5355,7 +5355,7 @@
         <v>194</v>
       </c>
       <c r="M219" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="220" spans="1:13" x14ac:dyDescent="0.4">
@@ -5363,7 +5363,7 @@
         <v>195</v>
       </c>
       <c r="M220" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="221" spans="1:13" x14ac:dyDescent="0.4">
@@ -5371,7 +5371,7 @@
         <v>196</v>
       </c>
       <c r="M221" s="7" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.4">
@@ -5379,7 +5379,7 @@
         <v>197</v>
       </c>
       <c r="M222" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.4">
@@ -5387,7 +5387,7 @@
         <v>198</v>
       </c>
       <c r="M223" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.4">
@@ -5395,50 +5395,50 @@
         <v>199</v>
       </c>
       <c r="M224" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="225" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L225" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A226" s="11" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="M226" s="7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.4">
@@ -5446,7 +5446,7 @@
         <v>200</v>
       </c>
       <c r="M227" s="7" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.4">
@@ -5454,7 +5454,7 @@
         <v>201</v>
       </c>
       <c r="M228" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.4">
@@ -5462,7 +5462,7 @@
         <v>202</v>
       </c>
       <c r="M229" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.4">
@@ -5470,7 +5470,7 @@
         <v>203</v>
       </c>
       <c r="M230" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.4">
@@ -5478,7 +5478,7 @@
         <v>204</v>
       </c>
       <c r="M231" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.4">
@@ -5486,7 +5486,7 @@
         <v>205</v>
       </c>
       <c r="M232" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.4">
@@ -5494,7 +5494,7 @@
         <v>206</v>
       </c>
       <c r="M233" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.4">
@@ -5502,7 +5502,7 @@
         <v>207</v>
       </c>
       <c r="M234" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="235" spans="1:13" x14ac:dyDescent="0.4">
@@ -5510,7 +5510,7 @@
         <v>208</v>
       </c>
       <c r="M235" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="236" spans="1:13" x14ac:dyDescent="0.4">
@@ -5518,7 +5518,7 @@
         <v>209</v>
       </c>
       <c r="M236" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="237" spans="1:13" x14ac:dyDescent="0.4">
@@ -5526,7 +5526,7 @@
         <v>210</v>
       </c>
       <c r="M237" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="238" spans="1:13" x14ac:dyDescent="0.4">
@@ -5534,7 +5534,7 @@
         <v>211</v>
       </c>
       <c r="M238" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="239" spans="1:13" x14ac:dyDescent="0.4">
@@ -5542,7 +5542,7 @@
         <v>212</v>
       </c>
       <c r="M239" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="240" spans="1:13" x14ac:dyDescent="0.4">
@@ -5550,7 +5550,7 @@
         <v>213</v>
       </c>
       <c r="M240" s="7" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="241" spans="1:13" x14ac:dyDescent="0.4">
@@ -5558,7 +5558,7 @@
         <v>214</v>
       </c>
       <c r="M241" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="242" spans="1:13" x14ac:dyDescent="0.4">
@@ -5566,7 +5566,7 @@
         <v>215</v>
       </c>
       <c r="M242" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="243" spans="1:13" x14ac:dyDescent="0.4">
@@ -5574,7 +5574,7 @@
         <v>216</v>
       </c>
       <c r="M243" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="244" spans="1:13" x14ac:dyDescent="0.4">
@@ -5582,7 +5582,7 @@
         <v>217</v>
       </c>
       <c r="M244" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="245" spans="1:13" x14ac:dyDescent="0.4">
@@ -5590,7 +5590,7 @@
         <v>218</v>
       </c>
       <c r="M245" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="246" spans="1:13" x14ac:dyDescent="0.4">
@@ -5598,7 +5598,7 @@
         <v>219</v>
       </c>
       <c r="M246" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="247" spans="1:13" x14ac:dyDescent="0.4">
@@ -5606,7 +5606,7 @@
         <v>220</v>
       </c>
       <c r="M247" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="248" spans="1:13" x14ac:dyDescent="0.4">
@@ -5614,7 +5614,7 @@
         <v>221</v>
       </c>
       <c r="M248" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="249" spans="1:13" x14ac:dyDescent="0.4">
@@ -5622,7 +5622,7 @@
         <v>222</v>
       </c>
       <c r="M249" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="250" spans="1:13" x14ac:dyDescent="0.4">
@@ -5630,7 +5630,7 @@
         <v>223</v>
       </c>
       <c r="M250" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="251" spans="1:13" x14ac:dyDescent="0.4">
@@ -5638,7 +5638,7 @@
         <v>224</v>
       </c>
       <c r="M251" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="252" spans="1:13" x14ac:dyDescent="0.4">
@@ -5646,7 +5646,7 @@
         <v>225</v>
       </c>
       <c r="M252" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="253" spans="1:13" x14ac:dyDescent="0.4">
@@ -5654,7 +5654,7 @@
         <v>226</v>
       </c>
       <c r="M253" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="254" spans="1:13" x14ac:dyDescent="0.4">
@@ -5662,7 +5662,7 @@
         <v>227</v>
       </c>
       <c r="M254" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="255" spans="1:13" x14ac:dyDescent="0.4">
@@ -5670,50 +5670,50 @@
         <v>228</v>
       </c>
       <c r="M255" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="256" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L256" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="257" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A257" s="6" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="M257" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="258" spans="1:13" x14ac:dyDescent="0.4">
@@ -5721,7 +5721,7 @@
         <v>229</v>
       </c>
       <c r="M258" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="259" spans="1:13" x14ac:dyDescent="0.4">
@@ -5729,7 +5729,7 @@
         <v>230</v>
       </c>
       <c r="M259" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="260" spans="1:13" x14ac:dyDescent="0.4">
@@ -5737,7 +5737,7 @@
         <v>231</v>
       </c>
       <c r="M260" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="261" spans="1:13" x14ac:dyDescent="0.4">
@@ -5745,7 +5745,7 @@
         <v>232</v>
       </c>
       <c r="M261" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="262" spans="1:13" x14ac:dyDescent="0.4">
@@ -5753,7 +5753,7 @@
         <v>233</v>
       </c>
       <c r="M262" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
     </row>
     <row r="263" spans="1:13" x14ac:dyDescent="0.4">
@@ -5761,7 +5761,7 @@
         <v>234</v>
       </c>
       <c r="M263" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="264" spans="1:13" x14ac:dyDescent="0.4">
@@ -5769,7 +5769,7 @@
         <v>235</v>
       </c>
       <c r="M264" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="265" spans="1:13" x14ac:dyDescent="0.4">
@@ -5777,7 +5777,7 @@
         <v>236</v>
       </c>
       <c r="M265" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="266" spans="1:13" x14ac:dyDescent="0.4">
@@ -5785,7 +5785,7 @@
         <v>0</v>
       </c>
       <c r="M266" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="267" spans="1:13" x14ac:dyDescent="0.4">
@@ -5793,7 +5793,7 @@
         <v>237</v>
       </c>
       <c r="M267" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="268" spans="1:13" x14ac:dyDescent="0.4">
@@ -5801,7 +5801,7 @@
         <v>238</v>
       </c>
       <c r="M268" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="269" spans="1:13" x14ac:dyDescent="0.4">
@@ -5809,7 +5809,7 @@
         <v>239</v>
       </c>
       <c r="M269" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="270" spans="1:13" x14ac:dyDescent="0.4">
@@ -5817,7 +5817,7 @@
         <v>240</v>
       </c>
       <c r="M270" s="7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="271" spans="1:13" x14ac:dyDescent="0.4">
@@ -5825,7 +5825,7 @@
         <v>241</v>
       </c>
       <c r="M271" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="272" spans="1:13" x14ac:dyDescent="0.4">
@@ -5833,7 +5833,7 @@
         <v>242</v>
       </c>
       <c r="M272" s="7" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="273" spans="1:13" x14ac:dyDescent="0.4">
@@ -5841,7 +5841,7 @@
         <v>243</v>
       </c>
       <c r="M273" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="274" spans="1:13" x14ac:dyDescent="0.4">
@@ -5849,7 +5849,7 @@
         <v>244</v>
       </c>
       <c r="M274" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="275" spans="1:13" x14ac:dyDescent="0.4">
@@ -5857,7 +5857,7 @@
         <v>245</v>
       </c>
       <c r="M275" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="276" spans="1:13" x14ac:dyDescent="0.4">
@@ -5865,7 +5865,7 @@
         <v>246</v>
       </c>
       <c r="M276" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="277" spans="1:13" x14ac:dyDescent="0.4">
@@ -5873,7 +5873,7 @@
         <v>247</v>
       </c>
       <c r="M277" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="278" spans="1:13" x14ac:dyDescent="0.4">
@@ -5881,7 +5881,7 @@
         <v>248</v>
       </c>
       <c r="M278" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="279" spans="1:13" x14ac:dyDescent="0.4">
@@ -5889,7 +5889,7 @@
         <v>249</v>
       </c>
       <c r="M279" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="280" spans="1:13" x14ac:dyDescent="0.4">
@@ -5897,7 +5897,7 @@
         <v>250</v>
       </c>
       <c r="M280" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="281" spans="1:13" x14ac:dyDescent="0.4">
@@ -5905,7 +5905,7 @@
         <v>251</v>
       </c>
       <c r="M281" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="282" spans="1:13" x14ac:dyDescent="0.4">
@@ -5913,7 +5913,7 @@
         <v>252</v>
       </c>
       <c r="M282" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="283" spans="1:13" x14ac:dyDescent="0.4">
@@ -5921,7 +5921,7 @@
         <v>253</v>
       </c>
       <c r="M283" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="284" spans="1:13" x14ac:dyDescent="0.4">
@@ -5929,7 +5929,7 @@
         <v>254</v>
       </c>
       <c r="M284" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="285" spans="1:13" x14ac:dyDescent="0.4">
@@ -5937,7 +5937,7 @@
         <v>255</v>
       </c>
       <c r="M285" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="286" spans="1:13" x14ac:dyDescent="0.4">
@@ -5945,50 +5945,50 @@
         <v>256</v>
       </c>
       <c r="M286" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="287" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L287" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="288" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A288" s="9" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="M288" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="289" spans="1:13" x14ac:dyDescent="0.4">
@@ -5996,7 +5996,7 @@
         <v>257</v>
       </c>
       <c r="M289" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="290" spans="1:13" x14ac:dyDescent="0.4">
@@ -6004,7 +6004,7 @@
         <v>258</v>
       </c>
       <c r="M290" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.4">
@@ -6012,7 +6012,7 @@
         <v>259</v>
       </c>
       <c r="M291" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.4">
@@ -6020,7 +6020,7 @@
         <v>260</v>
       </c>
       <c r="M292" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.4">
@@ -6028,7 +6028,7 @@
         <v>261</v>
       </c>
       <c r="M293" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.4">
@@ -6036,7 +6036,7 @@
         <v>262</v>
       </c>
       <c r="M294" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.4">
@@ -6044,7 +6044,7 @@
         <v>263</v>
       </c>
       <c r="M295" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.4">
@@ -6052,7 +6052,7 @@
         <v>264</v>
       </c>
       <c r="M296" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.4">
@@ -6060,7 +6060,7 @@
         <v>265</v>
       </c>
       <c r="M297" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.4">
@@ -6068,7 +6068,7 @@
         <v>266</v>
       </c>
       <c r="M298" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.4">
@@ -6076,7 +6076,7 @@
         <v>267</v>
       </c>
       <c r="M299" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.4">
@@ -6084,7 +6084,7 @@
         <v>268</v>
       </c>
       <c r="M300" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.4">
@@ -6092,7 +6092,7 @@
         <v>269</v>
       </c>
       <c r="M301" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.4">
@@ -6100,7 +6100,7 @@
         <v>270</v>
       </c>
       <c r="M302" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.4">
@@ -6108,7 +6108,7 @@
         <v>271</v>
       </c>
       <c r="M303" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.4">
@@ -6116,7 +6116,7 @@
         <v>272</v>
       </c>
       <c r="M304" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.4">
@@ -6124,7 +6124,7 @@
         <v>273</v>
       </c>
       <c r="M305" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.4">
@@ -6132,7 +6132,7 @@
         <v>274</v>
       </c>
       <c r="M306" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.4">
@@ -6140,7 +6140,7 @@
         <v>275</v>
       </c>
       <c r="M307" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.4">
@@ -6148,7 +6148,7 @@
         <v>276</v>
       </c>
       <c r="M308" s="7" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.4">
@@ -6156,7 +6156,7 @@
         <v>277</v>
       </c>
       <c r="M309" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.4">
@@ -6164,7 +6164,7 @@
         <v>278</v>
       </c>
       <c r="M310" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.4">
@@ -6172,7 +6172,7 @@
         <v>279</v>
       </c>
       <c r="M311" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.4">
@@ -6180,7 +6180,7 @@
         <v>280</v>
       </c>
       <c r="M312" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.4">
@@ -6188,7 +6188,7 @@
         <v>281</v>
       </c>
       <c r="M313" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.4">
@@ -6196,7 +6196,7 @@
         <v>282</v>
       </c>
       <c r="M314" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.4">
@@ -6204,7 +6204,7 @@
         <v>283</v>
       </c>
       <c r="M315" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.4">
@@ -6212,7 +6212,7 @@
         <v>284</v>
       </c>
       <c r="M316" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="317" spans="1:13" x14ac:dyDescent="0.4">
@@ -6220,50 +6220,50 @@
         <v>285</v>
       </c>
       <c r="M317" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="318" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L318" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="319" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A319" s="10" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="M319" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="320" spans="1:13" x14ac:dyDescent="0.4">
@@ -6271,7 +6271,7 @@
         <v>286</v>
       </c>
       <c r="M320" s="7" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="321" spans="1:13" x14ac:dyDescent="0.4">
@@ -6279,7 +6279,7 @@
         <v>287</v>
       </c>
       <c r="M321" s="7" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="322" spans="1:13" x14ac:dyDescent="0.4">
@@ -6287,7 +6287,7 @@
         <v>288</v>
       </c>
       <c r="M322" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="323" spans="1:13" x14ac:dyDescent="0.4">
@@ -6295,7 +6295,7 @@
         <v>289</v>
       </c>
       <c r="M323" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="324" spans="1:13" x14ac:dyDescent="0.4">
@@ -6303,7 +6303,7 @@
         <v>290</v>
       </c>
       <c r="M324" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="325" spans="1:13" x14ac:dyDescent="0.4">
@@ -6311,7 +6311,7 @@
         <v>291</v>
       </c>
       <c r="M325" s="7" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="326" spans="1:13" x14ac:dyDescent="0.4">
@@ -6319,7 +6319,7 @@
         <v>292</v>
       </c>
       <c r="M326" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="327" spans="1:13" x14ac:dyDescent="0.4">
@@ -6327,7 +6327,7 @@
         <v>293</v>
       </c>
       <c r="M327" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="328" spans="1:13" x14ac:dyDescent="0.4">
@@ -6335,7 +6335,7 @@
         <v>294</v>
       </c>
       <c r="M328" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="329" spans="1:13" x14ac:dyDescent="0.4">
@@ -6343,7 +6343,7 @@
         <v>295</v>
       </c>
       <c r="M329" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="330" spans="1:13" x14ac:dyDescent="0.4">
@@ -6351,7 +6351,7 @@
         <v>296</v>
       </c>
       <c r="M330" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="331" spans="1:13" x14ac:dyDescent="0.4">
@@ -6359,7 +6359,7 @@
         <v>297</v>
       </c>
       <c r="M331" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="332" spans="1:13" x14ac:dyDescent="0.4">
@@ -6367,7 +6367,7 @@
         <v>298</v>
       </c>
       <c r="M332" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="333" spans="1:13" x14ac:dyDescent="0.4">
@@ -6375,7 +6375,7 @@
         <v>299</v>
       </c>
       <c r="M333" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="334" spans="1:13" x14ac:dyDescent="0.4">
@@ -6383,7 +6383,7 @@
         <v>300</v>
       </c>
       <c r="M334" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="335" spans="1:13" x14ac:dyDescent="0.4">
@@ -6391,7 +6391,7 @@
         <v>301</v>
       </c>
       <c r="M335" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="336" spans="1:13" x14ac:dyDescent="0.4">
@@ -6399,7 +6399,7 @@
         <v>302</v>
       </c>
       <c r="M336" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
     </row>
     <row r="337" spans="1:13" x14ac:dyDescent="0.4">
@@ -6407,7 +6407,7 @@
         <v>303</v>
       </c>
       <c r="M337" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="338" spans="1:13" x14ac:dyDescent="0.4">
@@ -6415,7 +6415,7 @@
         <v>304</v>
       </c>
       <c r="M338" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="339" spans="1:13" x14ac:dyDescent="0.4">
@@ -6423,7 +6423,7 @@
         <v>305</v>
       </c>
       <c r="M339" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="340" spans="1:13" x14ac:dyDescent="0.4">
@@ -6431,7 +6431,7 @@
         <v>306</v>
       </c>
       <c r="M340" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="341" spans="1:13" x14ac:dyDescent="0.4">
@@ -6439,7 +6439,7 @@
         <v>307</v>
       </c>
       <c r="M341" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="342" spans="1:13" x14ac:dyDescent="0.4">
@@ -6447,7 +6447,7 @@
         <v>308</v>
       </c>
       <c r="M342" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="343" spans="1:13" x14ac:dyDescent="0.4">
@@ -6455,7 +6455,7 @@
         <v>309</v>
       </c>
       <c r="M343" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="344" spans="1:13" x14ac:dyDescent="0.4">
@@ -6463,7 +6463,7 @@
         <v>310</v>
       </c>
       <c r="M344" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="345" spans="1:13" x14ac:dyDescent="0.4">
@@ -6471,7 +6471,7 @@
         <v>311</v>
       </c>
       <c r="M345" s="7" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="346" spans="1:13" x14ac:dyDescent="0.4">
@@ -6479,7 +6479,7 @@
         <v>312</v>
       </c>
       <c r="M346" s="7" t="s">
-        <v>667</v>
+        <v>732</v>
       </c>
     </row>
     <row r="347" spans="1:13" x14ac:dyDescent="0.4">
@@ -6487,7 +6487,7 @@
         <v>313</v>
       </c>
       <c r="M347" s="7" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="348" spans="1:13" x14ac:dyDescent="0.4">
@@ -6495,50 +6495,50 @@
         <v>314</v>
       </c>
       <c r="M348" s="7" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
     </row>
     <row r="349" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="C349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="E349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="G349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="H349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="I349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="K349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="L349" s="8" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="350" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A350" s="11" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="M350" s="7" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="351" spans="1:13" x14ac:dyDescent="0.4">
@@ -6546,7 +6546,7 @@
         <v>315</v>
       </c>
       <c r="M351" s="7" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="352" spans="1:13" x14ac:dyDescent="0.4">
@@ -6554,7 +6554,7 @@
         <v>316</v>
       </c>
       <c r="M352" s="7" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="353" spans="1:13" x14ac:dyDescent="0.4">
@@ -6562,7 +6562,7 @@
         <v>317</v>
       </c>
       <c r="M353" s="7" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="354" spans="1:13" x14ac:dyDescent="0.4">
@@ -6570,7 +6570,7 @@
         <v>318</v>
       </c>
       <c r="M354" s="7" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="355" spans="1:13" x14ac:dyDescent="0.4">
@@ -6578,7 +6578,7 @@
         <v>319</v>
       </c>
       <c r="M355" s="7" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
     </row>
     <row r="356" spans="1:13" x14ac:dyDescent="0.4">
@@ -6586,7 +6586,7 @@
         <v>320</v>
       </c>
       <c r="M356" s="7" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="357" spans="1:13" x14ac:dyDescent="0.4">
@@ -6594,7 +6594,7 @@
         <v>321</v>
       </c>
       <c r="M357" s="7" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
     </row>
     <row r="358" spans="1:13" x14ac:dyDescent="0.4">
@@ -6602,7 +6602,7 @@
         <v>322</v>
       </c>
       <c r="M358" s="7" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
     <row r="359" spans="1:13" x14ac:dyDescent="0.4">
@@ -6610,7 +6610,7 @@
         <v>323</v>
       </c>
       <c r="M359" s="7" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
     </row>
     <row r="360" spans="1:13" x14ac:dyDescent="0.4">
@@ -6618,7 +6618,7 @@
         <v>324</v>
       </c>
       <c r="M360" s="7" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="361" spans="1:13" x14ac:dyDescent="0.4">
@@ -6626,7 +6626,7 @@
         <v>325</v>
       </c>
       <c r="M361" s="7" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="362" spans="1:13" x14ac:dyDescent="0.4">
@@ -6634,7 +6634,7 @@
         <v>326</v>
       </c>
       <c r="M362" s="7" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
     </row>
     <row r="363" spans="1:13" x14ac:dyDescent="0.4">
@@ -6642,7 +6642,7 @@
         <v>327</v>
       </c>
       <c r="M363" s="7" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="364" spans="1:13" x14ac:dyDescent="0.4">
@@ -6650,7 +6650,7 @@
         <v>328</v>
       </c>
       <c r="M364" s="7" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="365" spans="1:13" x14ac:dyDescent="0.4">
@@ -6658,7 +6658,7 @@
         <v>329</v>
       </c>
       <c r="M365" s="7" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
     </row>
     <row r="366" spans="1:13" x14ac:dyDescent="0.4">
@@ -6666,7 +6666,7 @@
         <v>330</v>
       </c>
       <c r="M366" s="7" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="367" spans="1:13" x14ac:dyDescent="0.4">
@@ -6674,7 +6674,7 @@
         <v>331</v>
       </c>
       <c r="M367" s="7" t="s">
-        <v>687</v>
+        <v>733</v>
       </c>
     </row>
     <row r="368" spans="1:13" x14ac:dyDescent="0.4">
@@ -6682,7 +6682,7 @@
         <v>332</v>
       </c>
       <c r="M368" s="7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="369" spans="1:13" x14ac:dyDescent="0.4">
@@ -6690,7 +6690,7 @@
         <v>333</v>
       </c>
       <c r="M369" s="7" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="370" spans="1:13" x14ac:dyDescent="0.4">
@@ -6698,7 +6698,7 @@
         <v>334</v>
       </c>
       <c r="M370" s="7" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="371" spans="1:13" x14ac:dyDescent="0.4">
@@ -6706,7 +6706,7 @@
         <v>335</v>
       </c>
       <c r="M371" s="7" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="372" spans="1:13" x14ac:dyDescent="0.4">
@@ -6714,7 +6714,7 @@
         <v>336</v>
       </c>
       <c r="M372" s="7" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="373" spans="1:13" x14ac:dyDescent="0.4">
@@ -6722,7 +6722,7 @@
         <v>337</v>
       </c>
       <c r="M373" s="7" t="s">
-        <v>693</v>
+        <v>737</v>
       </c>
     </row>
     <row r="374" spans="1:13" x14ac:dyDescent="0.4">
@@ -6730,7 +6730,7 @@
         <v>338</v>
       </c>
       <c r="M374" s="7" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
     <row r="375" spans="1:13" x14ac:dyDescent="0.4">
@@ -6738,7 +6738,7 @@
         <v>339</v>
       </c>
       <c r="M375" s="7" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="376" spans="1:13" x14ac:dyDescent="0.4">
@@ -6746,7 +6746,7 @@
         <v>340</v>
       </c>
       <c r="M376" s="7" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
     </row>
     <row r="377" spans="1:13" x14ac:dyDescent="0.4">
@@ -6754,7 +6754,7 @@
         <v>341</v>
       </c>
       <c r="M377" s="7" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
     </row>
     <row r="378" spans="1:13" x14ac:dyDescent="0.4">
@@ -6762,7 +6762,7 @@
         <v>342</v>
       </c>
       <c r="M378" s="7" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
     </row>
     <row r="379" spans="1:13" x14ac:dyDescent="0.4">
@@ -6770,48 +6770,48 @@
         <v>343</v>
       </c>
       <c r="M379" s="7" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="380" spans="1:13" s="8" customFormat="1" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="B380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="D380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="F380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="G380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="H380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="I380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="J380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="K380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="L380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="M380" s="8" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
